--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -28785,5456 +28647,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay II - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>256 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>230 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,573万
-$25,371/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,542万
-$24,869/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,534万
-$24,745/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,530万
-$24,684/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,519万
-$24,500/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,515万
-$24,437/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,508万
-$24,318/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,504万
-$24,256/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,500万
-$24,195/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,496万
-$24,135/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,489万
-$24,015/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,485万
-$23,955/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,482万
-$23,895/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,478万
-$23,835/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 406呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 423呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr"/>
-      <c r="E31" s="19" t="inlineStr"/>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 332呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr"/>
-      <c r="I31" s="19" t="inlineStr"/>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 321呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay II - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>290 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>76 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1426呎 (4+房)
-$4,634万
-$32,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 327呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr"/>
-      <c r="L6" s="19" t="inlineStr"/>
-      <c r="M6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$1,008万
-$23,166/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$1,005万
-$23,108/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$725万
-$22,724/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$1,003万
-$23,051/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$723万
-$22,668/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$1,000万
-$22,993/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-$721万
-$22,682/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$998万
-$22,936/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$720万
-$22,555/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$995万
-$22,878/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,023万
-$22,529/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$728万
-$22,347/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$718万
-$22,498/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$993万
-$22,823/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,020万
-$22,471/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$727万
-$22,294/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$716万
-$22,442/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$990万
-$22,763/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,018万
-$22,416/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$725万
-$22,236/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$714万
-$22,389/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$985万
-$22,653/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,013万
-$22,306/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$721万
-$22,126/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$711万
-$22,276/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,240万
-$25,728/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$980万
-$22,540/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,008万
-$22,194/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$718万
-$22,015/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$707万
-$22,163/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,237万
-$25,666/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$978万
-$22,483/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,005万
-$22,139/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$716万
-$21,960/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$705万
-$22,110/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,234万
-$25,602/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$976万
-$22,425/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,002万
-$22,081/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$714万
-$21,908/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$704万
-$22,053/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,231万
-$25,537/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 335呎 (1房)
-$699万
-$20,863/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$973万
-$22,372/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$1,000万
-$22,029/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$712万
-$21,850/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-$702万
-$22,069/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-$1,127万
-$24,346/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,228万
-$25,473/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 335呎 (1房)
-$697万
-$20,809/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$971万
-$22,315/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$998万
-$21,974/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$711万
-$21,798/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$700万
-$21,944/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-$1,124万
-$24,285/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 482呎 (2房)
-$1,392万
-$28,873/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 470呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 335呎 (1房)
-$695万
-$20,755/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$968万
-$22,260/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$995万
-$21,919/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$709万
-$21,742/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$698万
-$21,887/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-$1,122万
-$24,227/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>M | 251呎 (开放式)
-$593万
-$23,637/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr"/>
-      <c r="C26" s="19" t="inlineStr"/>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 472呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 335呎 (1房)
-$692万
-$20,654/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$964万
-$22,149/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$990万
-$21,808/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$705万
-$21,635/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$695万
-$21,781/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-$1,116万
-$24,106/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="inlineStr">
-        <is>
-          <t>M | 255呎 (开放式)
-$593万
-$23,255/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr"/>
-      <c r="C27" s="19" t="inlineStr"/>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 472呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 335呎 (1房)
-$690万
-$20,603/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-$961万
-$22,092/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-$988万
-$21,756/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-$704万
-$21,580/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 319呎 (1房)
-$693万
-$21,724/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-$1,113万
-$24,045/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M27" s="18" t="inlineStr">
-        <is>
-          <t>M | 255呎 (开放式)
-$592万
-$23,196/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr"/>
-      <c r="C28" s="19" t="inlineStr"/>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 472呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 256呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr"/>
-      <c r="C29" s="19" t="inlineStr"/>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 472呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 256呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="19" t="inlineStr"/>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 472呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 462呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 328呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 454呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 256呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr"/>
-      <c r="C31" s="19" t="inlineStr"/>
-      <c r="D31" s="19" t="inlineStr"/>
-      <c r="E31" s="19" t="inlineStr"/>
-      <c r="F31" s="19" t="inlineStr"/>
-      <c r="G31" s="19" t="inlineStr"/>
-      <c r="H31" s="19" t="inlineStr"/>
-      <c r="I31" s="19" t="inlineStr"/>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 326呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>K | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>L | 463呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>M | 256呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay II - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 491呎 (2房)
-$1,360万
-$27,699/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 307呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 308呎 (1房)
-$846万
-$27,468/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 494呎 (2房)
-$1,360万
-$27,530/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 491呎 (2房)
-$1,282万
-$26,102/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 307呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 307呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 308呎 (1房)
-$809万
-$26,266/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 494呎 (2房)
-$1,326万
-$26,834/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 491呎 (2房)
-$1,274万
-$25,955/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 307呎 (1房)
-$789万
-$25,700/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 307呎 (1房)
-$789万
-$25,700/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 307呎 (1房)
-$789万
-$25,700/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 494呎 (2房)
-$1,308万
-$26,474/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 491呎 (2房)
-$1,268万
-$25,825/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 307呎 (1房)
-$785万
-$25,570/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 307呎 (1房)
-$785万
-$25,570/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 308呎 (1房)
-$785万
-$25,487/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 494呎 (2房)
-$1,301万
-$26,342/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 453呎 (2房)
-$1,188万
-$26,225/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 308呎 (1房)
-$781万
-$25,360/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 308呎 (1房)
-$781万
-$25,360/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 308呎 (1房)
-$784万
-$25,445/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 456呎 (2房)
-$1,250万
-$27,412/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -28647,4 +28828,5456 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1573万
+$25,371/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1542万
+$24,869/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1534万
+$24,745/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1530万
+$24,684/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1519万
+$24,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1515万
+$24,437/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1508万
+$24,318/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1504万
+$24,256/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1500万
+$24,195/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1496万
+$24,135/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1489万
+$24,015/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1485万
+$23,955/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1482万
+$23,895/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1478万
+$23,835/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 406呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr"/>
+      <c r="E30" s="23" t="inlineStr"/>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr"/>
+      <c r="I30" s="23" t="inlineStr"/>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 321呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1426呎 (4+房)
+$4634万
+$32,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 327呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr"/>
+      <c r="L5" s="23" t="inlineStr"/>
+      <c r="M5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$1008万
+$23,166/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$1005万
+$23,108/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$725万
+$22,724/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$1003万
+$23,051/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$723万
+$22,668/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$1000万
+$22,993/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+$721万
+$22,682/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$998万
+$22,936/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$720万
+$22,555/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$995万
+$22,878/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1023万
+$22,529/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$728万
+$22,347/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$718万
+$22,498/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$993万
+$22,823/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1020万
+$22,471/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$727万
+$22,294/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$716万
+$22,442/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$990万
+$22,763/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1018万
+$22,416/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$725万
+$22,236/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$714万
+$22,389/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$985万
+$22,653/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1013万
+$22,306/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$721万
+$22,126/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$711万
+$22,276/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1240万
+$25,728/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$980万
+$22,540/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1008万
+$22,194/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$718万
+$22,015/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$707万
+$22,163/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1237万
+$25,666/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$978万
+$22,483/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1005万
+$22,139/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$716万
+$21,960/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$705万
+$22,110/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1234万
+$25,602/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$976万
+$22,425/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1002万
+$22,081/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$714万
+$21,908/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$704万
+$22,053/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1231万
+$25,537/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 335呎 (1房)
+$699万
+$20,863/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$973万
+$22,372/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$1000万
+$22,029/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$712万
+$21,850/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+$702万
+$22,069/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+$1127万
+$24,346/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1228万
+$25,473/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 335呎 (1房)
+$697万
+$20,809/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$971万
+$22,315/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$998万
+$21,974/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$711万
+$21,798/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$700万
+$21,944/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+$1124万
+$24,285/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 482呎 (2房)
+$1392万
+$28,873/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 335呎 (1房)
+$695万
+$20,755/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$968万
+$22,260/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$995万
+$21,919/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$709万
+$21,742/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$698万
+$21,887/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+$1122万
+$24,227/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>M | 251呎 (开放式)
+$593万
+$23,637/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr"/>
+      <c r="C25" s="23" t="inlineStr"/>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 335呎 (1房)
+$692万
+$20,654/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$964万
+$22,149/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$990万
+$21,808/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$705万
+$21,635/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$695万
+$21,781/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+$1116万
+$24,106/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>M | 255呎 (开放式)
+$593万
+$23,255/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr"/>
+      <c r="C26" s="23" t="inlineStr"/>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 335呎 (1房)
+$690万
+$20,603/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+$961万
+$22,092/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+$988万
+$21,756/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+$704万
+$21,580/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 319呎 (1房)
+$693万
+$21,724/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+$1113万
+$24,045/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>M | 255呎 (开放式)
+$592万
+$23,196/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr"/>
+      <c r="C27" s="23" t="inlineStr"/>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 256呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr"/>
+      <c r="C28" s="23" t="inlineStr"/>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 256呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr"/>
+      <c r="C29" s="23" t="inlineStr"/>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 462呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 328呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 454呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 256呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr"/>
+      <c r="C30" s="23" t="inlineStr"/>
+      <c r="D30" s="23" t="inlineStr"/>
+      <c r="E30" s="23" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr"/>
+      <c r="G30" s="23" t="inlineStr"/>
+      <c r="H30" s="23" t="inlineStr"/>
+      <c r="I30" s="23" t="inlineStr"/>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 326呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 463呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>M | 256呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 491呎 (2房)
+$1360万
+$27,699/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 307呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 308呎 (1房)
+$846万
+$27,468/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 494呎 (2房)
+$1360万
+$27,530/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 491呎 (2房)
+$1282万
+$26,102/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 307呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 307呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 308呎 (1房)
+$809万
+$26,266/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 494呎 (2房)
+$1326万
+$26,834/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 491呎 (2房)
+$1274万
+$25,955/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 307呎 (1房)
+$789万
+$25,700/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 307呎 (1房)
+$789万
+$25,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 307呎 (1房)
+$789万
+$25,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 494呎 (2房)
+$1308万
+$26,474/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 491呎 (2房)
+$1268万
+$25,825/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 307呎 (1房)
+$785万
+$25,570/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 307呎 (1房)
+$785万
+$25,570/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 308呎 (1房)
+$785万
+$25,487/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 494呎 (2房)
+$1301万
+$26,342/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 453呎 (2房)
+$1188万
+$26,225/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 308呎 (1房)
+$781万
+$25,360/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 308呎 (1房)
+$781万
+$25,360/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 308呎 (1房)
+$784万
+$25,445/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 456呎 (2房)
+$1250万
+$27,412/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>7213000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>22682</v>
+        <v>22611</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -32158,9 +32158,9 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>K | 318呎 (1房)
+          <t>K | 319呎 (1房)
 $721万
-$22,682/呎
+$22,611/呎
 (26年-04月)</t>
         </is>
       </c>
@@ -33222,7 +33222,7 @@
           <t>A | 482呎 (2房)
 $1228万
 $25,473/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">

--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -11843,38 +11843,30 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>15114000</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>24377</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L162" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K162" s="5" t="n">
+        <v>15114000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>24377</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -11883,7 +11875,7 @@
       </c>
       <c r="N162" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39887,7 +39879,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39897,7 +39889,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40066,7 +40058,7 @@
           <t>A | 620呎 (3房)
 $1573万
 $25,371/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -40675,7 +40667,7 @@
           <t>A | 620呎 (3房)
 $1542万
 $24,869/呎
-(26年-06月-18日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -41279,12 +41271,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1511万
+$24,377/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">

--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -16000,7 +16000,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -40058,7 +40058,7 @@
           <t>A | 620呎 (3房)
 $1573万
 $25,371/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -40667,7 +40667,7 @@
           <t>A | 620呎 (3房)
 $1542万
 $24,869/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -40841,7 +40841,7 @@
           <t>A | 620呎 (3房)
 $1534万
 $24,745/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -40928,7 +40928,7 @@
           <t>A | 620呎 (3房)
 $1530万
 $24,684/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -41015,7 +41015,7 @@
           <t>A | 620呎 (3房)
 $1523万
 $24,561/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -41102,7 +41102,7 @@
           <t>A | 620呎 (3房)
 $1519万
 $24,500/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -41189,7 +41189,7 @@
           <t>A | 620呎 (3房)
 $1515万
 $24,437/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -41276,7 +41276,7 @@
           <t>A | 620呎 (3房)
 $1511万
 $24,377/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -41363,7 +41363,7 @@
           <t>A | 620呎 (3房)
 $1508万
 $24,318/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -41450,7 +41450,7 @@
           <t>A | 620呎 (3房)
 $1504万
 $24,256/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -41537,7 +41537,7 @@
           <t>A | 620呎 (3房)
 $1500万
 $24,195/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -41624,7 +41624,7 @@
           <t>A | 620呎 (3房)
 $1496万
 $24,135/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -41711,7 +41711,7 @@
           <t>A | 620呎 (3房)
 $1489万
 $24,015/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -41798,7 +41798,7 @@
           <t>A | 620呎 (3房)
 $1485万
 $23,955/呎
-(26年-06月-28日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -41885,7 +41885,7 @@
           <t>A | 620呎 (3房)
 $1482万
 $23,895/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -41972,7 +41972,7 @@
           <t>A | 620呎 (3房)
 $1478万
 $23,835/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -42376,7 +42376,7 @@
           <t>A | 1426呎 (4+房)
 $4634万
 $32,500/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr"/>
@@ -42808,7 +42808,7 @@
           <t>G | 435呎 (2房)
 $1008万
 $23,166/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -42911,7 +42911,7 @@
           <t>G | 435呎 (2房)
 $1005万
 $23,108/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -42935,7 +42935,7 @@
           <t>K | 319呎 (1房)
 $725万
 $22,724/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -43014,7 +43014,7 @@
           <t>G | 435呎 (2房)
 $1003万
 $23,051/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -43038,7 +43038,7 @@
           <t>K | 319呎 (1房)
 $723万
 $22,668/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -43117,7 +43117,7 @@
           <t>G | 435呎 (2房)
 $1000万
 $22,993/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -43141,7 +43141,7 @@
           <t>K | 319呎 (1房)
 $721万
 $22,611/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -43220,7 +43220,7 @@
           <t>G | 435呎 (2房)
 $998万
 $22,936/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -43244,7 +43244,7 @@
           <t>K | 319呎 (1房)
 $720万
 $22,555/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -43323,7 +43323,7 @@
           <t>G | 435呎 (2房)
 $995万
 $22,878/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -43331,7 +43331,7 @@
           <t>H | 454呎 (2房)
 $1023万
 $22,529/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -43339,7 +43339,7 @@
           <t>J | 326呎 (1房)
 $728万
 $22,347/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -43347,7 +43347,7 @@
           <t>K | 319呎 (1房)
 $718万
 $22,498/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -43426,7 +43426,7 @@
           <t>G | 435呎 (2房)
 $993万
 $22,823/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -43434,7 +43434,7 @@
           <t>H | 454呎 (2房)
 $1020万
 $22,471/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -43442,7 +43442,7 @@
           <t>J | 326呎 (1房)
 $727万
 $22,294/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -43450,7 +43450,7 @@
           <t>K | 319呎 (1房)
 $716万
 $22,442/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -43529,7 +43529,7 @@
           <t>G | 435呎 (2房)
 $990万
 $22,763/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -43537,7 +43537,7 @@
           <t>H | 454呎 (2房)
 $1018万
 $22,416/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -43545,7 +43545,7 @@
           <t>J | 326呎 (1房)
 $725万
 $22,236/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -43553,7 +43553,7 @@
           <t>K | 319呎 (1房)
 $714万
 $22,389/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -43632,7 +43632,7 @@
           <t>G | 435呎 (2房)
 $985万
 $22,653/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -43640,7 +43640,7 @@
           <t>H | 454呎 (2房)
 $1013万
 $22,306/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -43648,7 +43648,7 @@
           <t>J | 326呎 (1房)
 $721万
 $22,126/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -43656,7 +43656,7 @@
           <t>K | 319呎 (1房)
 $711万
 $22,276/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -43790,7 +43790,7 @@
           <t>A | 482呎 (2房)
 $1240万
 $25,728/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -43838,7 +43838,7 @@
           <t>G | 435呎 (2房)
 $980万
 $22,540/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -43846,7 +43846,7 @@
           <t>H | 454呎 (2房)
 $1008万
 $22,194/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -43854,7 +43854,7 @@
           <t>J | 326呎 (1房)
 $718万
 $22,015/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -43862,7 +43862,7 @@
           <t>K | 319呎 (1房)
 $707万
 $22,163/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -43893,7 +43893,7 @@
           <t>A | 482呎 (2房)
 $1237万
 $25,666/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -43941,7 +43941,7 @@
           <t>G | 435呎 (2房)
 $978万
 $22,483/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -43949,7 +43949,7 @@
           <t>H | 454呎 (2房)
 $1005万
 $22,139/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -43957,7 +43957,7 @@
           <t>J | 326呎 (1房)
 $716万
 $21,960/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -43965,7 +43965,7 @@
           <t>K | 319呎 (1房)
 $705万
 $22,110/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -43996,7 +43996,7 @@
           <t>A | 482呎 (2房)
 $1234万
 $25,602/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -44044,7 +44044,7 @@
           <t>G | 435呎 (2房)
 $976万
 $22,425/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -44052,7 +44052,7 @@
           <t>H | 454呎 (2房)
 $1002万
 $22,081/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -44060,7 +44060,7 @@
           <t>J | 326呎 (1房)
 $714万
 $21,908/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -44068,7 +44068,7 @@
           <t>K | 319呎 (1房)
 $704万
 $22,053/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -44099,7 +44099,7 @@
           <t>A | 482呎 (2房)
 $1231万
 $25,537/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -44139,7 +44139,7 @@
           <t>F | 335呎 (1房)
 $699万
 $20,863/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -44147,7 +44147,7 @@
           <t>G | 435呎 (2房)
 $973万
 $22,372/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -44155,7 +44155,7 @@
           <t>H | 454呎 (2房)
 $1000万
 $22,029/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -44163,7 +44163,7 @@
           <t>J | 326呎 (1房)
 $712万
 $21,850/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -44171,7 +44171,7 @@
           <t>K | 318呎 (1房)
 $702万
 $22,069/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -44179,7 +44179,7 @@
           <t>L | 463呎 (2房)
 $1127万
 $24,346/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44202,7 +44202,7 @@
           <t>A | 482呎 (2房)
 $1228万
 $25,473/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -44242,7 +44242,7 @@
           <t>F | 335呎 (1房)
 $697万
 $20,809/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -44250,7 +44250,7 @@
           <t>G | 435呎 (2房)
 $971万
 $22,315/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -44258,7 +44258,7 @@
           <t>H | 454呎 (2房)
 $998万
 $21,974/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -44266,7 +44266,7 @@
           <t>J | 326呎 (1房)
 $711万
 $21,798/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -44274,7 +44274,7 @@
           <t>K | 319呎 (1房)
 $700万
 $21,944/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -44282,7 +44282,7 @@
           <t>L | 463呎 (2房)
 $1124万
 $24,285/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -44345,7 +44345,7 @@
           <t>F | 335呎 (1房)
 $695万
 $20,755/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -44353,7 +44353,7 @@
           <t>G | 435呎 (2房)
 $968万
 $22,260/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -44361,7 +44361,7 @@
           <t>H | 454呎 (2房)
 $995万
 $21,919/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -44369,7 +44369,7 @@
           <t>J | 326呎 (1房)
 $709万
 $21,742/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -44377,7 +44377,7 @@
           <t>K | 319呎 (1房)
 $698万
 $21,887/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -44385,7 +44385,7 @@
           <t>L | 463呎 (2房)
 $1122万
 $24,227/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -44393,7 +44393,7 @@
           <t>M | 251呎 (开放式)
 $593万
 $23,637/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -44434,7 +44434,7 @@
           <t>F | 335呎 (1房)
 $692万
 $20,654/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -44442,7 +44442,7 @@
           <t>G | 435呎 (2房)
 $964万
 $22,149/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -44450,7 +44450,7 @@
           <t>H | 454呎 (2房)
 $990万
 $21,808/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -44458,7 +44458,7 @@
           <t>J | 326呎 (1房)
 $705万
 $21,635/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -44466,7 +44466,7 @@
           <t>K | 319呎 (1房)
 $695万
 $21,781/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -44474,7 +44474,7 @@
           <t>L | 463呎 (2房)
 $1116万
 $24,106/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -44482,7 +44482,7 @@
           <t>M | 255呎 (开放式)
 $593万
 $23,255/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -44523,7 +44523,7 @@
           <t>F | 335呎 (1房)
 $690万
 $20,603/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -44531,7 +44531,7 @@
           <t>G | 435呎 (2房)
 $961万
 $22,092/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -44539,7 +44539,7 @@
           <t>H | 454呎 (2房)
 $988万
 $21,756/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -44547,7 +44547,7 @@
           <t>J | 326呎 (1房)
 $704万
 $21,580/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -44555,7 +44555,7 @@
           <t>K | 319呎 (1房)
 $693万
 $21,724/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -44563,7 +44563,7 @@
           <t>L | 463呎 (2房)
 $1113万
 $24,045/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -44571,7 +44571,7 @@
           <t>M | 255呎 (开放式)
 $592万
 $23,196/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -45029,7 +45029,7 @@
           <t>A | 491呎 (2房)
 $1360万
 $27,699/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -45045,7 +45045,7 @@
           <t>C | 308呎 (1房)
 $846万
 $27,468/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -45061,7 +45061,7 @@
           <t>E | 494呎 (2房)
 $1360万
 $27,530/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -45076,7 +45076,7 @@
           <t>A | 491呎 (2房)
 $1282万
 $26,102/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45100,7 +45100,7 @@
           <t>D | 308呎 (1房)
 $809万
 $26,266/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -45108,7 +45108,7 @@
           <t>E | 494呎 (2房)
 $1326万
 $26,834/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -45123,7 +45123,7 @@
           <t>A | 491呎 (2房)
 $1274万
 $25,955/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -45131,7 +45131,7 @@
           <t>B | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -45139,7 +45139,7 @@
           <t>C | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -45147,7 +45147,7 @@
           <t>D | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -45155,7 +45155,7 @@
           <t>E | 494呎 (2房)
 $1308万
 $26,474/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -45170,7 +45170,7 @@
           <t>A | 491呎 (2房)
 $1268万
 $25,825/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -45178,7 +45178,7 @@
           <t>B | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -45186,7 +45186,7 @@
           <t>C | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -45194,7 +45194,7 @@
           <t>D | 308呎 (1房)
 $785万
 $25,487/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -45202,7 +45202,7 @@
           <t>E | 494呎 (2房)
 $1301万
 $26,342/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -45217,7 +45217,7 @@
           <t>A | 453呎 (2房)
 $1188万
 $26,225/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -45225,7 +45225,7 @@
           <t>B | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -45233,7 +45233,7 @@
           <t>C | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -45241,7 +45241,7 @@
           <t>D | 308呎 (1房)
 $784万
 $25,445/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -45249,7 +45249,7 @@
           <t>E | 456呎 (2房)
 $1250万
 $27,412/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -40058,7 +40058,7 @@
           <t>A | 620呎 (3房)
 $1573万
 $25,371/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -40667,7 +40667,7 @@
           <t>A | 620呎 (3房)
 $1542万
 $24,869/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -40841,7 +40841,7 @@
           <t>A | 620呎 (3房)
 $1534万
 $24,745/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -40928,7 +40928,7 @@
           <t>A | 620呎 (3房)
 $1530万
 $24,684/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -41015,7 +41015,7 @@
           <t>A | 620呎 (3房)
 $1523万
 $24,561/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -41102,7 +41102,7 @@
           <t>A | 620呎 (3房)
 $1519万
 $24,500/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -41189,7 +41189,7 @@
           <t>A | 620呎 (3房)
 $1515万
 $24,437/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -41276,7 +41276,7 @@
           <t>A | 620呎 (3房)
 $1511万
 $24,377/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -41363,7 +41363,7 @@
           <t>A | 620呎 (3房)
 $1508万
 $24,318/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -41450,7 +41450,7 @@
           <t>A | 620呎 (3房)
 $1504万
 $24,256/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -41537,7 +41537,7 @@
           <t>A | 620呎 (3房)
 $1500万
 $24,195/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -41624,7 +41624,7 @@
           <t>A | 620呎 (3房)
 $1496万
 $24,135/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -41711,7 +41711,7 @@
           <t>A | 620呎 (3房)
 $1489万
 $24,015/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -41798,7 +41798,7 @@
           <t>A | 620呎 (3房)
 $1485万
 $23,955/呎
-(26年-07月)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -41885,7 +41885,7 @@
           <t>A | 620呎 (3房)
 $1482万
 $23,895/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -41972,7 +41972,7 @@
           <t>A | 620呎 (3房)
 $1478万
 $23,835/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -42376,7 +42376,7 @@
           <t>A | 1426呎 (4+房)
 $4634万
 $32,500/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr"/>
@@ -42808,7 +42808,7 @@
           <t>G | 435呎 (2房)
 $1008万
 $23,166/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -42911,7 +42911,7 @@
           <t>G | 435呎 (2房)
 $1005万
 $23,108/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -42935,7 +42935,7 @@
           <t>K | 319呎 (1房)
 $725万
 $22,724/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -43014,7 +43014,7 @@
           <t>G | 435呎 (2房)
 $1003万
 $23,051/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -43038,7 +43038,7 @@
           <t>K | 319呎 (1房)
 $723万
 $22,668/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -43117,7 +43117,7 @@
           <t>G | 435呎 (2房)
 $1000万
 $22,993/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -43141,7 +43141,7 @@
           <t>K | 319呎 (1房)
 $721万
 $22,611/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -43220,7 +43220,7 @@
           <t>G | 435呎 (2房)
 $998万
 $22,936/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -43244,7 +43244,7 @@
           <t>K | 319呎 (1房)
 $720万
 $22,555/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -43323,7 +43323,7 @@
           <t>G | 435呎 (2房)
 $995万
 $22,878/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -43331,7 +43331,7 @@
           <t>H | 454呎 (2房)
 $1023万
 $22,529/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -43339,7 +43339,7 @@
           <t>J | 326呎 (1房)
 $728万
 $22,347/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -43347,7 +43347,7 @@
           <t>K | 319呎 (1房)
 $718万
 $22,498/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -43426,7 +43426,7 @@
           <t>G | 435呎 (2房)
 $993万
 $22,823/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -43434,7 +43434,7 @@
           <t>H | 454呎 (2房)
 $1020万
 $22,471/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -43442,7 +43442,7 @@
           <t>J | 326呎 (1房)
 $727万
 $22,294/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -43450,7 +43450,7 @@
           <t>K | 319呎 (1房)
 $716万
 $22,442/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -43529,7 +43529,7 @@
           <t>G | 435呎 (2房)
 $990万
 $22,763/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -43537,7 +43537,7 @@
           <t>H | 454呎 (2房)
 $1018万
 $22,416/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -43545,7 +43545,7 @@
           <t>J | 326呎 (1房)
 $725万
 $22,236/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -43553,7 +43553,7 @@
           <t>K | 319呎 (1房)
 $714万
 $22,389/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -43632,7 +43632,7 @@
           <t>G | 435呎 (2房)
 $985万
 $22,653/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -43640,7 +43640,7 @@
           <t>H | 454呎 (2房)
 $1013万
 $22,306/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -43648,7 +43648,7 @@
           <t>J | 326呎 (1房)
 $721万
 $22,126/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -43656,7 +43656,7 @@
           <t>K | 319呎 (1房)
 $711万
 $22,276/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -43790,7 +43790,7 @@
           <t>A | 482呎 (2房)
 $1240万
 $25,728/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -43838,7 +43838,7 @@
           <t>G | 435呎 (2房)
 $980万
 $22,540/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -43846,7 +43846,7 @@
           <t>H | 454呎 (2房)
 $1008万
 $22,194/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -43854,7 +43854,7 @@
           <t>J | 326呎 (1房)
 $718万
 $22,015/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -43862,7 +43862,7 @@
           <t>K | 319呎 (1房)
 $707万
 $22,163/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -43893,7 +43893,7 @@
           <t>A | 482呎 (2房)
 $1237万
 $25,666/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -43941,7 +43941,7 @@
           <t>G | 435呎 (2房)
 $978万
 $22,483/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -43949,7 +43949,7 @@
           <t>H | 454呎 (2房)
 $1005万
 $22,139/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -43957,7 +43957,7 @@
           <t>J | 326呎 (1房)
 $716万
 $21,960/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -43965,7 +43965,7 @@
           <t>K | 319呎 (1房)
 $705万
 $22,110/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -43996,7 +43996,7 @@
           <t>A | 482呎 (2房)
 $1234万
 $25,602/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -44044,7 +44044,7 @@
           <t>G | 435呎 (2房)
 $976万
 $22,425/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -44052,7 +44052,7 @@
           <t>H | 454呎 (2房)
 $1002万
 $22,081/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -44060,7 +44060,7 @@
           <t>J | 326呎 (1房)
 $714万
 $21,908/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -44068,7 +44068,7 @@
           <t>K | 319呎 (1房)
 $704万
 $22,053/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -44099,7 +44099,7 @@
           <t>A | 482呎 (2房)
 $1231万
 $25,537/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -44139,7 +44139,7 @@
           <t>F | 335呎 (1房)
 $699万
 $20,863/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -44147,7 +44147,7 @@
           <t>G | 435呎 (2房)
 $973万
 $22,372/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -44155,7 +44155,7 @@
           <t>H | 454呎 (2房)
 $1000万
 $22,029/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -44163,7 +44163,7 @@
           <t>J | 326呎 (1房)
 $712万
 $21,850/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -44171,7 +44171,7 @@
           <t>K | 318呎 (1房)
 $702万
 $22,069/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -44179,7 +44179,7 @@
           <t>L | 463呎 (2房)
 $1127万
 $24,346/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44202,7 +44202,7 @@
           <t>A | 482呎 (2房)
 $1228万
 $25,473/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -44242,7 +44242,7 @@
           <t>F | 335呎 (1房)
 $697万
 $20,809/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -44250,7 +44250,7 @@
           <t>G | 435呎 (2房)
 $971万
 $22,315/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -44258,7 +44258,7 @@
           <t>H | 454呎 (2房)
 $998万
 $21,974/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -44266,7 +44266,7 @@
           <t>J | 326呎 (1房)
 $711万
 $21,798/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -44274,7 +44274,7 @@
           <t>K | 319呎 (1房)
 $700万
 $21,944/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -44282,7 +44282,7 @@
           <t>L | 463呎 (2房)
 $1124万
 $24,285/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -44345,7 +44345,7 @@
           <t>F | 335呎 (1房)
 $695万
 $20,755/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -44353,7 +44353,7 @@
           <t>G | 435呎 (2房)
 $968万
 $22,260/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -44361,7 +44361,7 @@
           <t>H | 454呎 (2房)
 $995万
 $21,919/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -44369,7 +44369,7 @@
           <t>J | 326呎 (1房)
 $709万
 $21,742/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -44377,7 +44377,7 @@
           <t>K | 319呎 (1房)
 $698万
 $21,887/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -44385,7 +44385,7 @@
           <t>L | 463呎 (2房)
 $1122万
 $24,227/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -44393,7 +44393,7 @@
           <t>M | 251呎 (开放式)
 $593万
 $23,637/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -44434,7 +44434,7 @@
           <t>F | 335呎 (1房)
 $692万
 $20,654/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -44442,7 +44442,7 @@
           <t>G | 435呎 (2房)
 $964万
 $22,149/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -44450,7 +44450,7 @@
           <t>H | 454呎 (2房)
 $990万
 $21,808/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -44458,7 +44458,7 @@
           <t>J | 326呎 (1房)
 $705万
 $21,635/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -44466,7 +44466,7 @@
           <t>K | 319呎 (1房)
 $695万
 $21,781/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -44474,7 +44474,7 @@
           <t>L | 463呎 (2房)
 $1116万
 $24,106/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -44482,7 +44482,7 @@
           <t>M | 255呎 (开放式)
 $593万
 $23,255/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -44523,7 +44523,7 @@
           <t>F | 335呎 (1房)
 $690万
 $20,603/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -44531,7 +44531,7 @@
           <t>G | 435呎 (2房)
 $961万
 $22,092/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -44539,7 +44539,7 @@
           <t>H | 454呎 (2房)
 $988万
 $21,756/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -44547,7 +44547,7 @@
           <t>J | 326呎 (1房)
 $704万
 $21,580/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -44555,7 +44555,7 @@
           <t>K | 319呎 (1房)
 $693万
 $21,724/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -44563,7 +44563,7 @@
           <t>L | 463呎 (2房)
 $1113万
 $24,045/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -44571,7 +44571,7 @@
           <t>M | 255呎 (开放式)
 $592万
 $23,196/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -45029,7 +45029,7 @@
           <t>A | 491呎 (2房)
 $1360万
 $27,699/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -45045,7 +45045,7 @@
           <t>C | 308呎 (1房)
 $846万
 $27,468/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -45061,7 +45061,7 @@
           <t>E | 494呎 (2房)
 $1360万
 $27,530/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -45076,7 +45076,7 @@
           <t>A | 491呎 (2房)
 $1282万
 $26,102/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45100,7 +45100,7 @@
           <t>D | 308呎 (1房)
 $809万
 $26,266/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -45108,7 +45108,7 @@
           <t>E | 494呎 (2房)
 $1326万
 $26,834/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -45123,7 +45123,7 @@
           <t>A | 491呎 (2房)
 $1274万
 $25,955/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -45131,7 +45131,7 @@
           <t>B | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -45139,7 +45139,7 @@
           <t>C | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -45147,7 +45147,7 @@
           <t>D | 307呎 (1房)
 $789万
 $25,700/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -45155,7 +45155,7 @@
           <t>E | 494呎 (2房)
 $1308万
 $26,474/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -45170,7 +45170,7 @@
           <t>A | 491呎 (2房)
 $1268万
 $25,825/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -45178,7 +45178,7 @@
           <t>B | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -45186,7 +45186,7 @@
           <t>C | 307呎 (1房)
 $785万
 $25,570/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -45194,7 +45194,7 @@
           <t>D | 308呎 (1房)
 $785万
 $25,487/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -45202,7 +45202,7 @@
           <t>E | 494呎 (2房)
 $1301万
 $26,342/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -45217,7 +45217,7 @@
           <t>A | 453呎 (2房)
 $1188万
 $26,225/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -45225,7 +45225,7 @@
           <t>B | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -45233,7 +45233,7 @@
           <t>C | 308呎 (1房)
 $781万
 $25,360/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -45241,7 +45241,7 @@
           <t>D | 308呎 (1房)
 $784万
 $25,445/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -45249,7 +45249,7 @@
           <t>E | 456呎 (2房)
 $1250万
 $27,412/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Miami Quay II.xlsx
+++ b/files/九龙-启德-Miami Quay II.xlsx
@@ -7683,38 +7683,30 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>15380000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>24806</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K102" s="5" t="n">
+        <v>15380000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>24806</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7723,7 +7715,7 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39879,7 +39871,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39889,7 +39881,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40749,12 +40741,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1538万
+$24,806/呎
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
